--- a/outputs/monitor_xlsx/20260416.xlsx
+++ b/outputs/monitor_xlsx/20260416.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2046,165 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1895</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17931</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1180</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4790</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1386</v>
+      </c>
+      <c r="J18" t="n">
+        <v>992</v>
+      </c>
+      <c r="K18" t="n">
+        <v>358</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8134</v>
+      </c>
+      <c r="M18" t="n">
+        <v>35645</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400919</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17.32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>645</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7013</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>2227</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-20179</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1199</v>
+      </c>
+      <c r="J19" t="n">
+        <v>27096</v>
+      </c>
+      <c r="K19" t="n">
+        <v>119</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34749</v>
+      </c>
+      <c r="M19" t="n">
+        <v>174942</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393708</v>
+      </c>
+      <c r="O19" t="n">
+        <v>16.58</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>721</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="F20" t="n">
+        <v>21809</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>3896</v>
+      </c>
+      <c r="H20" t="n">
+        <v>198</v>
+      </c>
+      <c r="I20" t="n">
+        <v>272</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1712</v>
+      </c>
+      <c r="K20" t="n">
+        <v>243</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8648</v>
+      </c>
+      <c r="M20" t="n">
+        <v>42049</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-160569</v>
+      </c>
+      <c r="O20" t="n">
+        <v>21.35</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
